--- a/Project 1 Data Quality Assessment/D1 Sensor health/outputs/plot_data/FigV15_pelt_event_id_data.xlsx
+++ b/Project 1 Data Quality Assessment/D1 Sensor health/outputs/plot_data/FigV15_pelt_event_id_data.xlsx
@@ -450,7 +450,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12">
@@ -587,7 +587,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13">
@@ -607,7 +607,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -617,7 +617,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
@@ -668,7 +668,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -718,7 +718,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -748,7 +748,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13">
@@ -768,7 +768,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
@@ -838,16 +838,16 @@
         <v>45913.95833333334</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5158200918373936</v>
+        <v>0.4931412412568824</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5158200918373936</v>
+        <v>0.4931412412568824</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.1726755923324035</v>
+        <v>-0.17378161863277</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3431444995049902</v>
+        <v>0.3193596226241124</v>
       </c>
     </row>
     <row r="3">
@@ -861,16 +861,16 @@
         <v>45913.95833333334</v>
       </c>
       <c r="D3" t="n">
-        <v>0.7632933145668308</v>
+        <v>0.7591101740812373</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.7632933145668308</v>
+        <v>-0.7591101740812373</v>
       </c>
       <c r="F3" t="n">
-        <v>0.297722626524661</v>
+        <v>0.2934833940140517</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.4655706880421697</v>
+        <v>-0.4656267800671856</v>
       </c>
     </row>
     <row r="4">
@@ -884,16 +884,16 @@
         <v>45927.95833333334</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8205768203295032</v>
+        <v>0.8153828278611603</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.8205768203295032</v>
+        <v>-0.8153828278611603</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3632777228559561</v>
+        <v>0.3580882988343473</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.4572990974735471</v>
+        <v>-0.4572945290268131</v>
       </c>
     </row>
     <row r="5">
@@ -901,22 +901,22 @@
         <v>3</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45915.08333333334</v>
+        <v>45915</v>
       </c>
       <c r="C5" s="2" t="n">
         <v>45927.95833333334</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3900723904476466</v>
+        <v>0.3979217678796365</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3900723904476466</v>
+        <v>0.3979217678796365</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.2882887358989925</v>
+        <v>-0.332437026059421</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1017836545486541</v>
+        <v>0.06548474182021545</v>
       </c>
     </row>
     <row r="6">
@@ -924,22 +924,22 @@
         <v>4</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45917.16666666666</v>
+        <v>45915.5</v>
       </c>
       <c r="C6" s="2" t="n">
         <v>45927.95833333334</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5750981264987785</v>
+        <v>0.1597502994061932</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5750981264987785</v>
+        <v>0.1597502994061932</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.06316404161709886</v>
+        <v>0.06548474182021545</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5119340848816796</v>
+        <v>0.2252350412264086</v>
       </c>
     </row>
     <row r="7">
@@ -947,22 +947,22 @@
         <v>5</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45918.45833333334</v>
+        <v>45920.125</v>
       </c>
       <c r="C7" s="2" t="n">
         <v>45927.95833333334</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2862815340227732</v>
+        <v>0.643403985119911</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.2862815340227732</v>
+        <v>-0.643403985119911</v>
       </c>
       <c r="F7" t="n">
-        <v>0.184235721473065</v>
+        <v>0.4275226498799135</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.1020458125497081</v>
+        <v>-0.2158813352399976</v>
       </c>
     </row>
     <row r="8">
@@ -970,22 +970,22 @@
         <v>6</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45919.58333333334</v>
+        <v>45921.20833333334</v>
       </c>
       <c r="C8" s="2" t="n">
         <v>45927.95833333334</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4198927622780005</v>
+        <v>0.408773926608988</v>
       </c>
       <c r="E8" t="n">
-        <v>0.4198927622780005</v>
+        <v>0.408773926608988</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0360626592278823</v>
+        <v>-0.3473531064259698</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4559554215058828</v>
+        <v>0.06142082018301823</v>
       </c>
     </row>
     <row r="9">
@@ -993,22 +993,22 @@
         <v>7</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45920.125</v>
+        <v>45917.16666666666</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>45927.95833333334</v>
+        <v>45941.95833333334</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6464336126857201</v>
+        <v>0.5721368403271689</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.6464336126857201</v>
+        <v>0.5721368403271689</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4309045764309947</v>
+        <v>-0.06673069967765587</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.2155290362547254</v>
+        <v>0.5054061406495131</v>
       </c>
     </row>
     <row r="10">
@@ -1016,22 +1016,22 @@
         <v>8</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45921.20833333334</v>
+        <v>45918.45833333334</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>45927.95833333334</v>
+        <v>45941.95833333334</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4154044196027283</v>
+        <v>0.2850778130702656</v>
       </c>
       <c r="E10" t="n">
-        <v>0.4154044196027283</v>
+        <v>-0.2850778130702656</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.3513840319266209</v>
+        <v>0.1841759625876228</v>
       </c>
       <c r="G10" t="n">
-        <v>0.06402038767610747</v>
+        <v>-0.1009018504826428</v>
       </c>
     </row>
     <row r="11">
@@ -1039,22 +1039,22 @@
         <v>9</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45915</v>
+        <v>45919.58333333334</v>
       </c>
       <c r="C11" s="2" t="n">
         <v>45941.95833333334</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4010633312282461</v>
+        <v>0.4155997002165725</v>
       </c>
       <c r="E11" t="n">
-        <v>0.4010633312282461</v>
+        <v>0.4155997002165725</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.3321898820492229</v>
+        <v>0.03666041979667854</v>
       </c>
       <c r="G11" t="n">
-        <v>0.06887344917902315</v>
+        <v>0.4522601200132511</v>
       </c>
     </row>
     <row r="12">
@@ -1068,16 +1068,16 @@
         <v>45983.95833333334</v>
       </c>
       <c r="D12" t="n">
-        <v>0.243639426635612</v>
+        <v>0.2434998739933465</v>
       </c>
       <c r="E12" t="n">
-        <v>0.243639426635612</v>
+        <v>0.2434998739933465</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.01244089902252504</v>
+        <v>-0.01586958592486474</v>
       </c>
       <c r="G12" t="n">
-        <v>0.2311985276130869</v>
+        <v>0.2276302880684818</v>
       </c>
     </row>
     <row r="13">
@@ -1091,16 +1091,16 @@
         <v>45983.95833333334</v>
       </c>
       <c r="D13" t="n">
-        <v>0.2000263322144551</v>
+        <v>0.197542614919015</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.2000263322144551</v>
+        <v>-0.197542614919015</v>
       </c>
       <c r="F13" t="n">
-        <v>0.178564371585083</v>
+        <v>0.1748002641108833</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.02146196062937213</v>
+        <v>-0.02274235080813166</v>
       </c>
     </row>
     <row r="14">
@@ -1114,16 +1114,16 @@
         <v>46011.95833333334</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3475999128954361</v>
+        <v>0.3417827635581813</v>
       </c>
       <c r="E14" t="n">
-        <v>0.3475999128954361</v>
+        <v>0.3417827635581813</v>
       </c>
       <c r="F14" t="n">
-        <v>0.02332230633335857</v>
+        <v>0.02121939319807785</v>
       </c>
       <c r="G14" t="n">
-        <v>0.3709222192287947</v>
+        <v>0.3630021567562592</v>
       </c>
     </row>
     <row r="15">
@@ -1137,16 +1137,16 @@
         <v>46039.95833333334</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6134455364840599</v>
+        <v>0.6076138218377471</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.6134455364840599</v>
+        <v>-0.6076138218377471</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3817123625360792</v>
+        <v>0.3758352760544663</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.2317331739479808</v>
+        <v>-0.2317785457832809</v>
       </c>
     </row>
     <row r="16">
@@ -1160,16 +1160,16 @@
         <v>46039.95833333334</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6572031167450663</v>
+        <v>0.6532341410857805</v>
       </c>
       <c r="E16" t="n">
-        <v>0.6572031167450663</v>
+        <v>0.6532341410857805</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.2317331739479808</v>
+        <v>-0.2317785457832809</v>
       </c>
       <c r="G16" t="n">
-        <v>0.4254699427970854</v>
+        <v>0.4214555953024997</v>
       </c>
     </row>
     <row r="17">
@@ -1183,16 +1183,16 @@
         <v>46039.95833333334</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6955391418769361</v>
+        <v>0.6867965222607518</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.6955391418769361</v>
+        <v>-0.6867965222607518</v>
       </c>
       <c r="F17" t="n">
-        <v>0.3761568798940023</v>
+        <v>0.3718043765915635</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.3193822619829337</v>
+        <v>-0.3149921456691883</v>
       </c>
     </row>
     <row r="18">
@@ -1206,16 +1206,16 @@
         <v>46039.95833333334</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3445613343741034</v>
+        <v>0.3382729309094548</v>
       </c>
       <c r="E18" t="n">
-        <v>0.3445613343741034</v>
+        <v>0.3382729309094548</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.1838144913859317</v>
+        <v>-0.1801556338825069</v>
       </c>
       <c r="G18" t="n">
-        <v>0.1607468429881717</v>
+        <v>0.1581172970269479</v>
       </c>
     </row>
     <row r="19">
@@ -1223,22 +1223,22 @@
         <v>17</v>
       </c>
       <c r="B19" s="2" t="n">
-        <v>46039.70833333334</v>
+        <v>46068.70833333334</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>46067.95833333334</v>
+        <v>46081.95833333334</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2337941622666019</v>
+        <v>0.5538093043118131</v>
       </c>
       <c r="E19" t="n">
-        <v>0.2337941622666019</v>
+        <v>-0.5538093043118131</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.1582752910888931</v>
+        <v>0.06695352192479072</v>
       </c>
       <c r="G19" t="n">
-        <v>0.07551887117770882</v>
+        <v>-0.4868557823870223</v>
       </c>
     </row>
     <row r="20">
@@ -1246,22 +1246,22 @@
         <v>18</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>46068.70833333334</v>
+        <v>46069.29166666666</v>
       </c>
       <c r="C20" s="2" t="n">
         <v>46081.95833333334</v>
       </c>
       <c r="D20" t="n">
-        <v>0.5585068719285696</v>
+        <v>0.6535908688321076</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.5585068719285696</v>
+        <v>0.6535908688321076</v>
       </c>
       <c r="F20" t="n">
-        <v>0.06876850116917936</v>
+        <v>-0.3900489568190081</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.4897383707593903</v>
+        <v>0.2635419120130995</v>
       </c>
     </row>
     <row r="21">
@@ -1269,22 +1269,22 @@
         <v>19</v>
       </c>
       <c r="B21" s="2" t="n">
-        <v>46069.29166666666</v>
+        <v>46071.70833333334</v>
       </c>
       <c r="C21" s="2" t="n">
         <v>46081.95833333334</v>
       </c>
       <c r="D21" t="n">
-        <v>0.6592334083291239</v>
+        <v>0.3172444063884139</v>
       </c>
       <c r="E21" t="n">
-        <v>0.6592334083291239</v>
+        <v>-0.3172444063884139</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.3924135652997704</v>
+        <v>0.1263991238010541</v>
       </c>
       <c r="G21" t="n">
-        <v>0.2668198430293535</v>
+        <v>-0.1908452825873598</v>
       </c>
     </row>
     <row r="22">
@@ -1292,22 +1292,22 @@
         <v>20</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>46071.70833333334</v>
+        <v>46075.25</v>
       </c>
       <c r="C22" s="2" t="n">
         <v>46081.95833333334</v>
       </c>
       <c r="D22" t="n">
-        <v>0.322258666952103</v>
+        <v>0.1314529220254233</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.322258666952103</v>
+        <v>0.1314529220254233</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1299599622736965</v>
+        <v>-0.06136467333582793</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.1922987046784065</v>
+        <v>0.07008824868959537</v>
       </c>
     </row>
     <row r="23">
@@ -1315,22 +1315,22 @@
         <v>21</v>
       </c>
       <c r="B23" s="2" t="n">
-        <v>46075.25</v>
+        <v>46080.25</v>
       </c>
       <c r="C23" s="2" t="n">
         <v>46081.95833333334</v>
       </c>
       <c r="D23" t="n">
-        <v>0.1353488810927381</v>
+        <v>0.4041051983163085</v>
       </c>
       <c r="E23" t="n">
-        <v>0.1353488810927381</v>
+        <v>-0.4041051983163085</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.06076272087001371</v>
+        <v>0.2550369555678566</v>
       </c>
       <c r="G23" t="n">
-        <v>0.07458616022272439</v>
+        <v>-0.1490682427484519</v>
       </c>
     </row>
     <row r="24">
@@ -1338,22 +1338,22 @@
         <v>22</v>
       </c>
       <c r="B24" s="2" t="n">
-        <v>46080.25</v>
+        <v>46069.20833333334</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>46081.95833333334</v>
+        <v>46095.95833333334</v>
       </c>
       <c r="D24" t="n">
-        <v>0.4113589358011648</v>
+        <v>0.7707004157007149</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.4113589358011648</v>
+        <v>0.7707004157007149</v>
       </c>
       <c r="F24" t="n">
-        <v>0.2593278468018367</v>
+        <v>-0.4868557823870223</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.1520310889993281</v>
+        <v>0.2838446333136926</v>
       </c>
     </row>
     <row r="25">
@@ -1361,22 +1361,22 @@
         <v>23</v>
       </c>
       <c r="B25" s="2" t="n">
-        <v>46069.20833333334</v>
+        <v>46070.83333333334</v>
       </c>
       <c r="C25" s="2" t="n">
         <v>46095.95833333334</v>
       </c>
       <c r="D25" t="n">
-        <v>0.7771724063863553</v>
+        <v>0.2423318903132907</v>
       </c>
       <c r="E25" t="n">
-        <v>0.7771724063863553</v>
+        <v>-0.2423318903132907</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.4897383707593903</v>
+        <v>0.2730438913744563</v>
       </c>
       <c r="G25" t="n">
-        <v>0.287434035626965</v>
+        <v>0.03071200106116554</v>
       </c>
     </row>
     <row r="26">
@@ -1384,22 +1384,22 @@
         <v>24</v>
       </c>
       <c r="B26" s="2" t="n">
-        <v>46070.83333333334</v>
+        <v>46074.25</v>
       </c>
       <c r="C26" s="2" t="n">
         <v>46095.95833333334</v>
       </c>
       <c r="D26" t="n">
-        <v>0.2436412886694504</v>
+        <v>0.2581588739851532</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.2436412886694504</v>
+        <v>0.2581588739851532</v>
       </c>
       <c r="F26" t="n">
-        <v>0.2763785488100777</v>
+        <v>-0.2049805510341916</v>
       </c>
       <c r="G26" t="n">
-        <v>0.03273726014062725</v>
+        <v>0.05317832295096161</v>
       </c>
     </row>
     <row r="27">
@@ -1407,22 +1407,22 @@
         <v>25</v>
       </c>
       <c r="B27" s="2" t="n">
-        <v>46074.25</v>
+        <v>46080.20833333334</v>
       </c>
       <c r="C27" s="2" t="n">
         <v>46095.95833333334</v>
       </c>
       <c r="D27" t="n">
-        <v>0.2619358550114403</v>
+        <v>0.4108635695472733</v>
       </c>
       <c r="E27" t="n">
-        <v>0.2619358550114403</v>
+        <v>-0.4108635695472733</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.2042363344239957</v>
+        <v>0.2656817386448884</v>
       </c>
       <c r="G27" t="n">
-        <v>0.05769952058744467</v>
+        <v>-0.145181830902385</v>
       </c>
     </row>
     <row r="28">
@@ -1436,16 +1436,16 @@
         <v>46109.95833333334</v>
       </c>
       <c r="D28" t="n">
-        <v>0.8475706100983305</v>
+        <v>0.8422797830226973</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.8475706100983305</v>
+        <v>-0.8422797830226973</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.09517874994829972</v>
+        <v>-0.0938435365229261</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.9427493600466302</v>
+        <v>-0.9361233195456234</v>
       </c>
     </row>
     <row r="29">
@@ -1459,16 +1459,16 @@
         <v>46109.95833333334</v>
       </c>
       <c r="D29" t="n">
-        <v>1.145310689325161</v>
+        <v>1.130274070580795</v>
       </c>
       <c r="E29" t="n">
-        <v>1.145310689325161</v>
+        <v>1.130274070580795</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.4604741177517395</v>
+        <v>-0.4516988946401774</v>
       </c>
       <c r="G29" t="n">
-        <v>0.6848365715734213</v>
+        <v>0.6785751759406172</v>
       </c>
     </row>
     <row r="30">
@@ -1482,16 +1482,16 @@
         <v>46109.95833333334</v>
       </c>
       <c r="D30" t="n">
-        <v>0.482444813167461</v>
+        <v>0.4847209874514191</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.482444813167461</v>
+        <v>-0.4847209874514191</v>
       </c>
       <c r="F30" t="n">
-        <v>0.7028392696070024</v>
+        <v>0.6960131592264877</v>
       </c>
       <c r="G30" t="n">
-        <v>0.2203944564395413</v>
+        <v>0.2112921717750686</v>
       </c>
     </row>
   </sheetData>

--- a/Project 1 Data Quality Assessment/D1 Sensor health/outputs/plot_data/FigV15_pelt_event_id_data.xlsx
+++ b/Project 1 Data Quality Assessment/D1 Sensor health/outputs/plot_data/FigV15_pelt_event_id_data.xlsx
@@ -450,7 +450,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">

--- a/Project 1 Data Quality Assessment/D1 Sensor health/outputs/plot_data/FigV15_pelt_event_id_data.xlsx
+++ b/Project 1 Data Quality Assessment/D1 Sensor health/outputs/plot_data/FigV15_pelt_event_id_data.xlsx
@@ -450,7 +450,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-8fdd3599890f</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">

--- a/Project 1 Data Quality Assessment/D1 Sensor health/outputs/plot_data/FigV15_pelt_event_id_data.xlsx
+++ b/Project 1 Data Quality Assessment/D1 Sensor health/outputs/plot_data/FigV15_pelt_event_id_data.xlsx
@@ -450,7 +450,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>d1-final-8fdd3599890f</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
